--- a/fine_tuning_excel_pack_brand_voice/02_validation_holdout_brand_voice_UTF8_FIXED.xlsx
+++ b/fine_tuning_excel_pack_brand_voice/02_validation_holdout_brand_voice_UTF8_FIXED.xlsx
@@ -8,22 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\baitap\NT114\NT114-Git\NT114.Q21-Web-Copy-Writing\fine_tuning_excel_pack_brand_voice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{294EE3B8-3557-4C36-AE72-E8C14C900E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{431B3F2D-DBFB-4FB5-AD0B-9725600E652B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2244" yWindow="2052" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2244" yWindow="2052" windowWidth="17280" windowHeight="8880" xr2:uid="{0308CC48-84C2-4A81-A9DE-6CA1662BB7B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Validation" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="81">
-  <si>
-    <t>example_id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="60">
   <si>
     <t>input</t>
   </si>
@@ -41,9 +57,6 @@
   </si>
   <si>
     <t>product</t>
-  </si>
-  <si>
-    <t>EX-001</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -70,17 +83,17 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Headline: máy pha cà phê capsule cho người thích cà phê nhanh tại nhà
-Subheadline: Lựa chọn thực tế với pha nhanh; dễ vệ sinh; thiết kế gọn; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 2:
-Headline: máy pha cà phê capsule cho người thích cà phê nhanh tại nhà
-Subheadline: Lựa chọn thực tế với pha nhanh; dễ vệ sinh; thiết kế gọn; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 3:
-Headline: máy pha cà phê capsule cho người thích cà phê nhanh tại nhà
-Subheadline: Lựa chọn thực tế với pha nhanh; dễ vệ sinh; thiết kế gọn; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.</t>
+Headline: Giải pháp rõ ràng cho máy pha cà phê capsule cho người thích cà phê nhanh tại nhà với pha nhanh.
+Subheadline: Tập trung vào dễ vệ sinh và thiết kế gọn, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
+Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
+Phiên bản 2:
+Headline: máy pha cà phê capsule là lựa chọn đáng cân nhắc cho người thích cà phê nhanh tại nhà.
+Subheadline: Điểm mạnh nằm ở dễ vệ sinh, pha nhanh và tặng hộp capsule dùng thử để bạn so sánh dễ hơn.
+Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
+Phiên bản 3:
+Headline: Tối ưu gọn gàng cho máy pha cà phê capsule nếu bạn cần pha nhanh và dễ vệ sinh.
+Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
   </si>
   <si>
     <t>ecommerce</t>
@@ -93,9 +106,6 @@
   </si>
   <si>
     <t>máy pha cà phê capsule</t>
-  </si>
-  <si>
-    <t>EX-002</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -123,29 +133,38 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Mô tả ngắn: máy pha cà phê capsule dành cho người thích cà phê nhanh tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 2:
-Mô tả ngắn: máy pha cà phê capsule dành cho người thích cà phê nhanh tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Mô tả ngắn: máy pha cà phê capsule dành cho người thích cà phê nhanh tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.</t>
+Mô tả ngắn: máy pha cà phê capsule dành cho người thích cà phê nhanh tại nhà, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+Lợi ích chính:
+- Hỗ trợ nhu cầu thực tế nhờ pha nhanh và dễ vệ sinh.
+- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và tặng hộp capsule dùng thử.
+Đặc điểm nổi bật:
+- pha nhanh.
+- thiết kế gọn.
+Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn là người thích cà phê nhanh tại nhà, máy pha cà phê capsule là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+Lợi ích chính:
+- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
+- Tập trung vào dễ vệ sinh và thiết kế gọn để phục vụ dùng hằng ngày.
+Đặc điểm nổi bật:
+- dễ vệ sinh.
+- tặng hộp capsule dùng thử.
+Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
+Phiên bản 3:
+Mô tả ngắn: máy pha cà phê capsule giúp người thích cà phê nhanh tại nhà có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
+Lợi ích chính:
+- thiết kế gọn làm cho việc dùng tiện hơn.
+- pha nhanh hỗ trợ đúng mối quan tâm chính.
+Đặc điểm nổi bật:
+- pha nhanh.
+- dễ vệ sinh.
+Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
   </si>
   <si>
     <t>friendly</t>
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>EX-003</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -173,29 +192,26 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Hook: người thích cà phê nhanh tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: máy pha cà phê capsule giúp việc hằng ngày nhẹ hơn nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng hộp capsule dùng thử.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 2:
-Hook: người thích cà phê nhanh tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: máy pha cà phê capsule giúp việc hằng ngày nhẹ hơn nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng hộp capsule dùng thử.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 3:
-Hook: người thích cà phê nhanh tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: máy pha cà phê capsule giúp việc hằng ngày nhẹ hơn nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng hộp capsule dùng thử.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.</t>
+Hook: Lựa chọn ấm áp hơn cho người thích cà phê nhanh tại nhà.
+Caption: máy pha cà phê capsule giúp việc hằng ngày nhẹ hơn nhờ pha nhanh, dễ vệ sinh và thiết kế gọn. Hiện có tặng hộp capsule dùng thử, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
+Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
+Hashtags: #MayPhaCa #NguoiThichCa #PhaNhanh
+Phiên bản 2:
+Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người thích cà phê nhanh tại nhà.
+Caption: Với dễ vệ sinh và thiết kế gọn, máy pha cà phê capsule cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng hộp capsule dùng thử là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
+Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
+Hashtags: #MayPhaCa #DeVeSinh #MuaSamThongMinh
+Phiên bản 3:
+Hook: Một cách để yên tâm hơn cho người thích cà phê nhanh tại nhà một lựa chọn gọn gàng hơn.
+Caption: Khi xem máy pha cà phê capsule, hãy chú ý vào pha nhanh, dễ vệ sinh và thiết kế gọn. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
+Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
+Hashtags: #MayPhaCa #ThietKeGon #ThuongMaiDienTu</t>
   </si>
   <si>
     <t>emotional</t>
   </si>
   <si>
     <t>social</t>
-  </si>
-  <si>
-    <t>EX-004</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -224,29 +240,29 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Subject: Gợi ý máy pha cà phê capsule cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích cà phê nhanh tại nhà; máy pha cà phê capsule có thể là lựa chọn đáng cân nhắc nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Ưu đãi hiện có: tặng hộp capsule dùng thử.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 2:
-Subject: Gợi ý máy pha cà phê capsule cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích cà phê nhanh tại nhà; máy pha cà phê capsule có thể là lựa chọn đáng cân nhắc nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Ưu đãi hiện có: tặng hộp capsule dùng thử.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 3:
-Subject: Gợi ý máy pha cà phê capsule cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích cà phê nhanh tại nhà; máy pha cà phê capsule có thể là lựa chọn đáng cân nhắc nhờ pha nhanh; dễ vệ sinh; thiết kế gọn. Ưu đãi hiện có: tặng hộp capsule dùng thử.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.</t>
+Subject: Gợi ý máy pha cà phê capsule cho người thích cà phê nhanh tại nhà
+Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+Lời chào: Chào bạn,
+Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, máy pha cà phê capsule có các điểm nổi bật như pha nhanh, dễ vệ sinh và thiết kế gọn. Hiện có tặng hộp capsule dùng thử, nên bạn có thể xem thêm thông tin trước khi quyết định.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
+Phiên bản 2:
+Subject: máy pha cà phê capsule có thể hợp với nhu cầu của bạn
+Preview text: Một vài lý do để người thích cà phê nhanh tại nhà cân nhắc sản phẩm này.
+Lời chào: Chào bạn,
+Nội dung chính: máy pha cà phê capsule tập trung vào dễ vệ sinh, pha nhanh và thiết kế gọn. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. tặng hộp capsule dùng thử giúp bạn có thêm lý do so sánh.
+Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
+Phiên bản 3:
+Subject: Xem nhanh máy pha cà phê capsule trước khi bạn chọn
+Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Lời chào: Chào bạn,
+Nội dung chính: Với người thích cà phê nhanh tại nhà, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. máy pha cà phê capsule có pha nhanh, dễ vệ sinh và thiết kế gọn; ngoài ra còn có tặng hộp capsule dùng thử để bạn cân nhắc thêm.
+Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
   </si>
   <si>
     <t>urgent</t>
   </si>
   <si>
     <t>email</t>
-  </si>
-  <si>
-    <t>EX-005</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -273,23 +289,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Headline: kem chống nắng nâng tông nhẹ cho người đi làm cần lớp nền tự nhiên
-Subheadline: Lựa chọn thực tế với thấm nhanh; không bí da; dùng hằng ngày; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 2:
-Headline: kem chống nắng nâng tông nhẹ cho người đi làm cần lớp nền tự nhiên
-Subheadline: Lựa chọn thực tế với thấm nhanh; không bí da; dùng hằng ngày; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 3:
-Headline: kem chống nắng nâng tông nhẹ cho người đi làm cần lớp nền tự nhiên
-Subheadline: Lựa chọn thực tế với thấm nhanh; không bí da; dùng hằng ngày; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.</t>
+Headline: Giải pháp rõ ràng cho kem chống nắng nâng tông nhẹ cho người đi làm cần lớp nền tự nhiên với thấm nhanh.
+Subheadline: Tập trung vào không bí da và dùng hằng ngày, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
+Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
+Phiên bản 2:
+Headline: kem chống nắng nâng tông nhẹ là lựa chọn đáng cân nhắc cho người đi làm cần lớp nền tự nhiên.
+Subheadline: Điểm mạnh nằm ở không bí da, thấm nhanh và mua 2 tặng 1 minisize để bạn so sánh dễ hơn.
+Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
+Phiên bản 3:
+Headline: Tối ưu gọn gàng cho kem chống nắng nâng tông nhẹ nếu bạn cần thấm nhanh và không bí da.
+Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
   </si>
   <si>
     <t>kem chống nắng nâng tông nhẹ</t>
-  </si>
-  <si>
-    <t>EX-006</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -317,23 +330,32 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Mô tả ngắn: kem chống nắng nâng tông nhẹ dành cho người đi làm cần lớp nền tự nhiên; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ thấm nhanh; không bí da; dùng hằng ngày. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 2:
-Mô tả ngắn: kem chống nắng nâng tông nhẹ dành cho người đi làm cần lớp nền tự nhiên; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ thấm nhanh; không bí da; dùng hằng ngày. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Mô tả ngắn: kem chống nắng nâng tông nhẹ dành cho người đi làm cần lớp nền tự nhiên; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ thấm nhanh; không bí da; dùng hằng ngày. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-007</t>
+Mô tả ngắn: kem chống nắng nâng tông nhẹ dành cho người đi làm cần lớp nền tự nhiên, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+Lợi ích chính:
+- Hỗ trợ nhu cầu thực tế nhờ thấm nhanh và không bí da.
+- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và mua 2 tặng 1 minisize.
+Đặc điểm nổi bật:
+- thấm nhanh.
+- dùng hằng ngày.
+Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn là người đi làm cần lớp nền tự nhiên, kem chống nắng nâng tông nhẹ là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+Lợi ích chính:
+- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
+- Tập trung vào không bí da và dùng hằng ngày để phục vụ dùng hằng ngày.
+Đặc điểm nổi bật:
+- không bí da.
+- mua 2 tặng 1 minisize.
+Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
+Phiên bản 3:
+Mô tả ngắn: kem chống nắng nâng tông nhẹ giúp người đi làm cần lớp nền tự nhiên có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
+Lợi ích chính:
+- dùng hằng ngày làm cho việc dùng tiện hơn.
+- thấm nhanh hỗ trợ đúng mối quan tâm chính.
+Đặc điểm nổi bật:
+- thấm nhanh.
+- không bí da.
+Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -361,23 +383,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Hook: người đi làm cần lớp nền tự nhiên thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kem chống nắng nâng tông nhẹ giúp việc hằng ngày nhẹ hơn nhờ thấm nhanh; không bí da; dùng hằng ngày. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: mua 2 tặng 1 minisize.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 2:
-Hook: người đi làm cần lớp nền tự nhiên thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kem chống nắng nâng tông nhẹ giúp việc hằng ngày nhẹ hơn nhờ thấm nhanh; không bí da; dùng hằng ngày. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: mua 2 tặng 1 minisize.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 3:
-Hook: người đi làm cần lớp nền tự nhiên thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kem chống nắng nâng tông nhẹ giúp việc hằng ngày nhẹ hơn nhờ thấm nhanh; không bí da; dùng hằng ngày. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: mua 2 tặng 1 minisize.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.</t>
-  </si>
-  <si>
-    <t>EX-008</t>
+Hook: Lựa chọn ấm áp hơn cho người đi làm cần lớp nền tự nhiên.
+Caption: kem chống nắng nâng tông nhẹ giúp việc hằng ngày nhẹ hơn nhờ thấm nhanh, không bí da và dùng hằng ngày. Hiện có mua 2 tặng 1 minisize, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
+Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
+Hashtags: #KemChongNang #NguoiDiLam #ThamNhanh
+Phiên bản 2:
+Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người đi làm cần lớp nền tự nhiên.
+Caption: Với không bí da và dùng hằng ngày, kem chống nắng nâng tông nhẹ cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. mua 2 tặng 1 minisize là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
+Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
+Hashtags: #KemChongNang #KhongBiDa #MuaSamThongMinh
+Phiên bản 3:
+Hook: Một cách để yên tâm hơn cho người đi làm cần lớp nền tự nhiên một lựa chọn gọn gàng hơn.
+Caption: Khi xem kem chống nắng nâng tông nhẹ, hãy chú ý vào thấm nhanh, không bí da và dùng hằng ngày. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
+Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
+Hashtags: #KemChongNang #DungHangNgay #ThuongMaiDienTu</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -406,23 +425,23 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Subject: Gợi ý kem chống nắng nâng tông nhẹ cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người đi làm cần lớp nền tự nhiên; kem chống nắng nâng tông nhẹ có thể là lựa chọn đáng cân nhắc nhờ thấm nhanh; không bí da; dùng hằng ngày. Ưu đãi hiện có: mua 2 tặng 1 minisize.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 2:
-Subject: Gợi ý kem chống nắng nâng tông nhẹ cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người đi làm cần lớp nền tự nhiên; kem chống nắng nâng tông nhẹ có thể là lựa chọn đáng cân nhắc nhờ thấm nhanh; không bí da; dùng hằng ngày. Ưu đãi hiện có: mua 2 tặng 1 minisize.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 3:
-Subject: Gợi ý kem chống nắng nâng tông nhẹ cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người đi làm cần lớp nền tự nhiên; kem chống nắng nâng tông nhẹ có thể là lựa chọn đáng cân nhắc nhờ thấm nhanh; không bí da; dùng hằng ngày. Ưu đãi hiện có: mua 2 tặng 1 minisize.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-009</t>
+Subject: Gợi ý kem chống nắng nâng tông nhẹ cho người đi làm cần lớp nền tự nhiên
+Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+Lời chào: Chào bạn,
+Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, kem chống nắng nâng tông nhẹ có các điểm nổi bật như thấm nhanh, không bí da và dùng hằng ngày. Hiện có mua 2 tặng 1 minisize, nên bạn có thể xem thêm thông tin trước khi quyết định.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
+Phiên bản 2:
+Subject: kem chống nắng nâng tông nhẹ có thể hợp với nhu cầu của bạn
+Preview text: Một vài lý do để người đi làm cần lớp nền tự nhiên cân nhắc sản phẩm này.
+Lời chào: Chào bạn,
+Nội dung chính: kem chống nắng nâng tông nhẹ tập trung vào không bí da, thấm nhanh và dùng hằng ngày. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. mua 2 tặng 1 minisize giúp bạn có thêm lý do so sánh.
+Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
+Phiên bản 3:
+Subject: Xem nhanh kem chống nắng nâng tông nhẹ trước khi bạn chọn
+Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Lời chào: Chào bạn,
+Nội dung chính: Với người đi làm cần lớp nền tự nhiên, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. kem chống nắng nâng tông nhẹ có thấm nhanh, không bí da và dùng hằng ngày; ngoài ra còn có mua 2 tặng 1 minisize để bạn cân nhắc thêm.
+Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -449,23 +468,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Headline: kệ sách lắp ghép cho người ở căn hộ nhỏ
-Subheadline: Lựa chọn thực tế với dễ lắp; tối ưu góc trống; màu trung tính; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 2:
-Headline: kệ sách lắp ghép cho người ở căn hộ nhỏ
-Subheadline: Lựa chọn thực tế với dễ lắp; tối ưu góc trống; màu trung tính; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 3:
-Headline: kệ sách lắp ghép cho người ở căn hộ nhỏ
-Subheadline: Lựa chọn thực tế với dễ lắp; tối ưu góc trống; màu trung tính; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.</t>
+Headline: Giải pháp rõ ràng cho kệ sách lắp ghép cho người ở căn hộ nhỏ với dễ lắp.
+Subheadline: Tập trung vào tối ưu góc trống và màu trung tính, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
+Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
+Phiên bản 2:
+Headline: kệ sách lắp ghép là lựa chọn đáng cân nhắc cho người ở căn hộ nhỏ.
+Subheadline: Điểm mạnh nằm ở tối ưu góc trống, dễ lắp và hỗ trợ hướng dẫn lắp đặt để bạn so sánh dễ hơn.
+Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
+Phiên bản 3:
+Headline: Tối ưu gọn gàng cho kệ sách lắp ghép nếu bạn cần dễ lắp và tối ưu góc trống.
+Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
   </si>
   <si>
     <t>kệ sách lắp ghép</t>
-  </si>
-  <si>
-    <t>EX-010</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -493,23 +509,32 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Mô tả ngắn: kệ sách lắp ghép dành cho người ở căn hộ nhỏ; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ dễ lắp; tối ưu góc trống; màu trung tính. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 2:
-Mô tả ngắn: kệ sách lắp ghép dành cho người ở căn hộ nhỏ; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ dễ lắp; tối ưu góc trống; màu trung tính. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Mô tả ngắn: kệ sách lắp ghép dành cho người ở căn hộ nhỏ; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ dễ lắp; tối ưu góc trống; màu trung tính. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-011</t>
+Mô tả ngắn: kệ sách lắp ghép dành cho người ở căn hộ nhỏ, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+Lợi ích chính:
+- Hỗ trợ nhu cầu thực tế nhờ dễ lắp và tối ưu góc trống.
+- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và hỗ trợ hướng dẫn lắp đặt.
+Đặc điểm nổi bật:
+- dễ lắp.
+- màu trung tính.
+Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn là người ở căn hộ nhỏ, kệ sách lắp ghép là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+Lợi ích chính:
+- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
+- Tập trung vào tối ưu góc trống và màu trung tính để phục vụ dùng hằng ngày.
+Đặc điểm nổi bật:
+- tối ưu góc trống.
+- hỗ trợ hướng dẫn lắp đặt.
+Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
+Phiên bản 3:
+Mô tả ngắn: kệ sách lắp ghép giúp người ở căn hộ nhỏ có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
+Lợi ích chính:
+- màu trung tính làm cho việc dùng tiện hơn.
+- dễ lắp hỗ trợ đúng mối quan tâm chính.
+Đặc điểm nổi bật:
+- dễ lắp.
+- tối ưu góc trống.
+Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -537,23 +562,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Hook: người ở căn hộ nhỏ thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kệ sách lắp ghép giúp việc hằng ngày nhẹ hơn nhờ dễ lắp; tối ưu góc trống; màu trung tính. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: hỗ trợ hướng dẫn lắp đặt.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 2:
-Hook: người ở căn hộ nhỏ thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kệ sách lắp ghép giúp việc hằng ngày nhẹ hơn nhờ dễ lắp; tối ưu góc trống; màu trung tính. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: hỗ trợ hướng dẫn lắp đặt.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 3:
-Hook: người ở căn hộ nhỏ thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: kệ sách lắp ghép giúp việc hằng ngày nhẹ hơn nhờ dễ lắp; tối ưu góc trống; màu trung tính. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: hỗ trợ hướng dẫn lắp đặt.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.</t>
-  </si>
-  <si>
-    <t>EX-012</t>
+Hook: Lựa chọn ấm áp hơn cho người ở căn hộ nhỏ.
+Caption: kệ sách lắp ghép giúp việc hằng ngày nhẹ hơn nhờ dễ lắp, tối ưu góc trống và màu trung tính. Hiện có hỗ trợ hướng dẫn lắp đặt, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
+Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
+Hashtags: #KeSachLap #NguoiOCan #DeLap
+Phiên bản 2:
+Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người ở căn hộ nhỏ.
+Caption: Với tối ưu góc trống và màu trung tính, kệ sách lắp ghép cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. hỗ trợ hướng dẫn lắp đặt là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
+Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
+Hashtags: #KeSachLap #ToiUuGoc #MuaSamThongMinh
+Phiên bản 3:
+Hook: Một cách để yên tâm hơn cho người ở căn hộ nhỏ một lựa chọn gọn gàng hơn.
+Caption: Khi xem kệ sách lắp ghép, hãy chú ý vào dễ lắp, tối ưu góc trống và màu trung tính. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
+Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
+Hashtags: #KeSachLap #MauTrungTinh #ThuongMaiDienTu</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -582,23 +604,23 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Subject: Gợi ý kệ sách lắp ghép cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người ở căn hộ nhỏ; kệ sách lắp ghép có thể là lựa chọn đáng cân nhắc nhờ dễ lắp; tối ưu góc trống; màu trung tính. Ưu đãi hiện có: hỗ trợ hướng dẫn lắp đặt.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 2:
-Subject: Gợi ý kệ sách lắp ghép cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người ở căn hộ nhỏ; kệ sách lắp ghép có thể là lựa chọn đáng cân nhắc nhờ dễ lắp; tối ưu góc trống; màu trung tính. Ưu đãi hiện có: hỗ trợ hướng dẫn lắp đặt.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 3:
-Subject: Gợi ý kệ sách lắp ghép cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người ở căn hộ nhỏ; kệ sách lắp ghép có thể là lựa chọn đáng cân nhắc nhờ dễ lắp; tối ưu góc trống; màu trung tính. Ưu đãi hiện có: hỗ trợ hướng dẫn lắp đặt.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-013</t>
+Subject: Gợi ý kệ sách lắp ghép cho người ở căn hộ nhỏ
+Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+Lời chào: Chào bạn,
+Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, kệ sách lắp ghép có các điểm nổi bật như dễ lắp, tối ưu góc trống và màu trung tính. Hiện có hỗ trợ hướng dẫn lắp đặt, nên bạn có thể xem thêm thông tin trước khi quyết định.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
+Phiên bản 2:
+Subject: kệ sách lắp ghép có thể hợp với nhu cầu của bạn
+Preview text: Một vài lý do để người ở căn hộ nhỏ cân nhắc sản phẩm này.
+Lời chào: Chào bạn,
+Nội dung chính: kệ sách lắp ghép tập trung vào tối ưu góc trống, dễ lắp và màu trung tính. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. hỗ trợ hướng dẫn lắp đặt giúp bạn có thêm lý do so sánh.
+Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
+Phiên bản 3:
+Subject: Xem nhanh kệ sách lắp ghép trước khi bạn chọn
+Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Lời chào: Chào bạn,
+Nội dung chính: Với người ở căn hộ nhỏ, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. kệ sách lắp ghép có dễ lắp, tối ưu góc trống và màu trung tính; ngoài ra còn có hỗ trợ hướng dẫn lắp đặt để bạn cân nhắc thêm.
+Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -625,23 +647,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Headline: bộ dao bếp inox cho người nấu ăn tại nhà
-Subheadline: Lựa chọn thực tế với cầm chắc tay; dễ rửa; đủ size cơ bản; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 2:
-Headline: bộ dao bếp inox cho người nấu ăn tại nhà
-Subheadline: Lựa chọn thực tế với cầm chắc tay; dễ rửa; đủ size cơ bản; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 3:
-Headline: bộ dao bếp inox cho người nấu ăn tại nhà
-Subheadline: Lựa chọn thực tế với cầm chắc tay; dễ rửa; đủ size cơ bản; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.</t>
+Headline: Giải pháp rõ ràng cho bộ dao bếp inox cho người nấu ăn tại nhà với cầm chắc tay.
+Subheadline: Tập trung vào dễ rửa và đủ size cơ bản, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
+Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
+Phiên bản 2:
+Headline: bộ dao bếp inox là lựa chọn đáng cân nhắc cho người nấu ăn tại nhà.
+Subheadline: Điểm mạnh nằm ở dễ rửa, cầm chắc tay và tặng thanh mài dao để bạn so sánh dễ hơn.
+Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
+Phiên bản 3:
+Headline: Tối ưu gọn gàng cho bộ dao bếp inox nếu bạn cần cầm chắc tay và dễ rửa.
+Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
   </si>
   <si>
     <t>bộ dao bếp inox</t>
-  </si>
-  <si>
-    <t>EX-014</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -669,23 +688,32 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Mô tả ngắn: bộ dao bếp inox dành cho người nấu ăn tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 2:
-Mô tả ngắn: bộ dao bếp inox dành cho người nấu ăn tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Mô tả ngắn: bộ dao bếp inox dành cho người nấu ăn tại nhà; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-015</t>
+Mô tả ngắn: bộ dao bếp inox dành cho người nấu ăn tại nhà, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+Lợi ích chính:
+- Hỗ trợ nhu cầu thực tế nhờ cầm chắc tay và dễ rửa.
+- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và tặng thanh mài dao.
+Đặc điểm nổi bật:
+- cầm chắc tay.
+- đủ size cơ bản.
+Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn là người nấu ăn tại nhà, bộ dao bếp inox là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+Lợi ích chính:
+- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
+- Tập trung vào dễ rửa và đủ size cơ bản để phục vụ dùng hằng ngày.
+Đặc điểm nổi bật:
+- dễ rửa.
+- tặng thanh mài dao.
+Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
+Phiên bản 3:
+Mô tả ngắn: bộ dao bếp inox giúp người nấu ăn tại nhà có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
+Lợi ích chính:
+- đủ size cơ bản làm cho việc dùng tiện hơn.
+- cầm chắc tay hỗ trợ đúng mối quan tâm chính.
+Đặc điểm nổi bật:
+- cầm chắc tay.
+- dễ rửa.
+Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -713,23 +741,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Hook: người nấu ăn tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: bộ dao bếp inox giúp việc hằng ngày nhẹ hơn nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng thanh mài dao.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 2:
-Hook: người nấu ăn tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: bộ dao bếp inox giúp việc hằng ngày nhẹ hơn nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng thanh mài dao.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 3:
-Hook: người nấu ăn tại nhà thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: bộ dao bếp inox giúp việc hằng ngày nhẹ hơn nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: tặng thanh mài dao.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.</t>
-  </si>
-  <si>
-    <t>EX-016</t>
+Hook: Lựa chọn ấm áp hơn cho người nấu ăn tại nhà.
+Caption: bộ dao bếp inox giúp việc hằng ngày nhẹ hơn nhờ cầm chắc tay, dễ rửa và đủ size cơ bản. Hiện có tặng thanh mài dao, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
+Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
+Hashtags: #BoDaoBep #NguoiNauAn #CamChacTay
+Phiên bản 2:
+Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người nấu ăn tại nhà.
+Caption: Với dễ rửa và đủ size cơ bản, bộ dao bếp inox cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng thanh mài dao là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
+Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
+Hashtags: #BoDaoBep #DeRua #MuaSamThongMinh
+Phiên bản 3:
+Hook: Một cách để yên tâm hơn cho người nấu ăn tại nhà một lựa chọn gọn gàng hơn.
+Caption: Khi xem bộ dao bếp inox, hãy chú ý vào cầm chắc tay, dễ rửa và đủ size cơ bản. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
+Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
+Hashtags: #BoDaoBep #DuSizeCo #ThuongMaiDienTu</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -758,23 +783,23 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Subject: Gợi ý bộ dao bếp inox cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người nấu ăn tại nhà; bộ dao bếp inox có thể là lựa chọn đáng cân nhắc nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Ưu đãi hiện có: tặng thanh mài dao.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 2:
-Subject: Gợi ý bộ dao bếp inox cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người nấu ăn tại nhà; bộ dao bếp inox có thể là lựa chọn đáng cân nhắc nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Ưu đãi hiện có: tặng thanh mài dao.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 3:
-Subject: Gợi ý bộ dao bếp inox cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người nấu ăn tại nhà; bộ dao bếp inox có thể là lựa chọn đáng cân nhắc nhờ cầm chắc tay; dễ rửa; đủ size cơ bản. Ưu đãi hiện có: tặng thanh mài dao.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-017</t>
+Subject: Gợi ý bộ dao bếp inox cho người nấu ăn tại nhà
+Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+Lời chào: Chào bạn,
+Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, bộ dao bếp inox có các điểm nổi bật như cầm chắc tay, dễ rửa và đủ size cơ bản. Hiện có tặng thanh mài dao, nên bạn có thể xem thêm thông tin trước khi quyết định.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
+Phiên bản 2:
+Subject: bộ dao bếp inox có thể hợp với nhu cầu của bạn
+Preview text: Một vài lý do để người nấu ăn tại nhà cân nhắc sản phẩm này.
+Lời chào: Chào bạn,
+Nội dung chính: bộ dao bếp inox tập trung vào dễ rửa, cầm chắc tay và đủ size cơ bản. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. tặng thanh mài dao giúp bạn có thêm lý do so sánh.
+Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
+Phiên bản 3:
+Subject: Xem nhanh bộ dao bếp inox trước khi bạn chọn
+Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Lời chào: Chào bạn,
+Nội dung chính: Với người nấu ăn tại nhà, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. bộ dao bếp inox có cầm chắc tay, dễ rửa và đủ size cơ bản; ngoài ra còn có tặng thanh mài dao để bạn cân nhắc thêm.
+Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -801,23 +826,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Headline: loa bluetooth chống nước cho người thích nghe nhạc khi du lịch
-Subheadline: Lựa chọn thực tế với chống nước nhẹ; âm lượng ổn định; pin dùng lâu; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 2:
-Headline: loa bluetooth chống nước cho người thích nghe nhạc khi du lịch
-Subheadline: Lựa chọn thực tế với chống nước nhẹ; âm lượng ổn định; pin dùng lâu; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.
-Phiên bản 3:
-Headline: loa bluetooth chống nước cho người thích nghe nhạc khi du lịch
-Subheadline: Lựa chọn thực tế với chống nước nhẹ; âm lượng ổn định; pin dùng lâu; giữ giọng tin cậy và gọn ý.
-CTA: Xem lựa chọn phù hợp hôm nay.</t>
+Headline: Giải pháp rõ ràng cho loa bluetooth chống nước cho người thích nghe nhạc khi du lịch với chống nước nhẹ.
+Subheadline: Tập trung vào âm lượng ổn định và pin dùng lâu, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
+Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
+Phiên bản 2:
+Headline: loa bluetooth chống nước là lựa chọn đáng cân nhắc cho người thích nghe nhạc khi du lịch.
+Subheadline: Điểm mạnh nằm ở âm lượng ổn định, chống nước nhẹ và bảo hành 6 tháng để bạn so sánh dễ hơn.
+Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
+Phiên bản 3:
+Headline: Tối ưu gọn gàng cho loa bluetooth chống nước nếu bạn cần chống nước nhẹ và âm lượng ổn định.
+Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
   </si>
   <si>
     <t>loa bluetooth chống nước</t>
-  </si>
-  <si>
-    <t>EX-018</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -845,23 +867,32 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Mô tả ngắn: loa bluetooth chống nước dành cho người thích nghe nhạc khi du lịch; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 2:
-Mô tả ngắn: loa bluetooth chống nước dành cho người thích nghe nhạc khi du lịch; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Mô tả ngắn: loa bluetooth chống nước dành cho người thích nghe nhạc khi du lịch; tập trung vào trải nghiệm dùng hằng ngày và thông tin rõ ràng.
-Lợi ích chính: - Hỗ trợ nhu cầu thực tế nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. - Dễ bắt đầu và dễ duy trì trong sinh hoạt thường ngày.
-Điểm cần biết: Nội dung không bịa chứng nhận hay con số ngoài brief.
-CTA: Nhắn tin để được tư vấn lựa chọn phù hợp.</t>
-  </si>
-  <si>
-    <t>EX-019</t>
+Mô tả ngắn: loa bluetooth chống nước dành cho người thích nghe nhạc khi du lịch, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+Lợi ích chính:
+- Hỗ trợ nhu cầu thực tế nhờ chống nước nhẹ và âm lượng ổn định.
+- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và bảo hành 6 tháng.
+Đặc điểm nổi bật:
+- chống nước nhẹ.
+- pin dùng lâu.
+Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn là người thích nghe nhạc khi du lịch, loa bluetooth chống nước là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+Lợi ích chính:
+- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
+- Tập trung vào âm lượng ổn định và pin dùng lâu để phục vụ dùng hằng ngày.
+Đặc điểm nổi bật:
+- âm lượng ổn định.
+- bảo hành 6 tháng.
+Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
+Phiên bản 3:
+Mô tả ngắn: loa bluetooth chống nước giúp người thích nghe nhạc khi du lịch có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
+Lợi ích chính:
+- pin dùng lâu làm cho việc dùng tiện hơn.
+- chống nước nhẹ hỗ trợ đúng mối quan tâm chính.
+Đặc điểm nổi bật:
+- chống nước nhẹ.
+- âm lượng ổn định.
+Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -889,23 +920,20 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Hook: người thích nghe nhạc khi du lịch thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: loa bluetooth chống nước giúp việc hằng ngày nhẹ hơn nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: bảo hành 6 tháng.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 2:
-Hook: người thích nghe nhạc khi du lịch thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: loa bluetooth chống nước giúp việc hằng ngày nhẹ hơn nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: bảo hành 6 tháng.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.
-Phiên bản 3:
-Hook: người thích nghe nhạc khi du lịch thường cần một lựa chọn đơn giản mà dùng được lâu.
-Caption: loa bluetooth chống nước giúp việc hằng ngày nhẹ hơn nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Giọng viết rõ lợi ích; không nói quá và không tạo cảm giác ép mua.
-Ưu đãi: bảo hành 6 tháng.
-CTA: Lưu lại hoặc nhắn shop để hỏi thêm trước khi chọn.</t>
-  </si>
-  <si>
-    <t>EX-020</t>
+Hook: Lựa chọn ấm áp hơn cho người thích nghe nhạc khi du lịch.
+Caption: loa bluetooth chống nước giúp việc hằng ngày nhẹ hơn nhờ chống nước nhẹ, âm lượng ổn định và pin dùng lâu. Hiện có bảo hành 6 tháng, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
+Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
+Hashtags: #LoaBluetoothChong #NguoiThichNghe #ChongNuocNhe
+Phiên bản 2:
+Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người thích nghe nhạc khi du lịch.
+Caption: Với âm lượng ổn định và pin dùng lâu, loa bluetooth chống nước cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. bảo hành 6 tháng là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
+Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
+Hashtags: #LoaBluetoothChong #AmLuongOn #MuaSamThongMinh
+Phiên bản 3:
+Hook: Một cách để yên tâm hơn cho người thích nghe nhạc khi du lịch một lựa chọn gọn gàng hơn.
+Caption: Khi xem loa bluetooth chống nước, hãy chú ý vào chống nước nhẹ, âm lượng ổn định và pin dùng lâu. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
+Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
+Hashtags: #LoaBluetoothChong #PinDungLau #ThuongMaiDienTu</t>
   </si>
   <si>
     <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
@@ -934,43 +962,71 @@
   </si>
   <si>
     <t>Phiên bản 1:
-Subject: Gợi ý loa bluetooth chống nước cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích nghe nhạc khi du lịch; loa bluetooth chống nước có thể là lựa chọn đáng cân nhắc nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Ưu đãi hiện có: bảo hành 6 tháng.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 2:
-Subject: Gợi ý loa bluetooth chống nước cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích nghe nhạc khi du lịch; loa bluetooth chống nước có thể là lựa chọn đáng cân nhắc nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Ưu đãi hiện có: bảo hành 6 tháng.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.
-Phiên bản 3:
-Subject: Gợi ý loa bluetooth chống nước cho nhu cầu hằng ngày
-Preview text: Thông tin ngắn gọn để bạn cân nhắc trước khi mua.
-Nội dung chính: Nếu bạn là người thích nghe nhạc khi du lịch; loa bluetooth chống nước có thể là lựa chọn đáng cân nhắc nhờ chống nước nhẹ; âm lượng ổn định; pin dùng lâu. Ưu đãi hiện có: bảo hành 6 tháng.
-CTA: Xem chi tiết và chọn phiên bản phù hợp.</t>
+Subject: Gợi ý loa bluetooth chống nước cho người thích nghe nhạc khi du lịch
+Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+Lời chào: Chào bạn,
+Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, loa bluetooth chống nước có các điểm nổi bật như chống nước nhẹ, âm lượng ổn định và pin dùng lâu. Hiện có bảo hành 6 tháng, nên bạn có thể xem thêm thông tin trước khi quyết định.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
+Phiên bản 2:
+Subject: loa bluetooth chống nước có thể hợp với nhu cầu của bạn
+Preview text: Một vài lý do để người thích nghe nhạc khi du lịch cân nhắc sản phẩm này.
+Lời chào: Chào bạn,
+Nội dung chính: loa bluetooth chống nước tập trung vào âm lượng ổn định, chống nước nhẹ và pin dùng lâu. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. bảo hành 6 tháng giúp bạn có thêm lý do so sánh.
+Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
+Phiên bản 3:
+Subject: Xem nhanh loa bluetooth chống nước trước khi bạn chọn
+Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Lời chào: Chào bạn,
+Nội dung chính: Với người thích nghe nhạc khi du lịch, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. loa bluetooth chống nước có chống nước nhẹ, âm lượng ổn định và pin dùng lâu; ngoài ra còn có bảo hành 6 tháng để bạn cân nhắc thêm.
+Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -985,14 +1041,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1326,500 +1383,438 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6A3B5A-C3E4-4AEE-BCC2-6B7D7159B191}">
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="72" customWidth="1"/>
-    <col min="4" max="7" width="14" customWidth="1"/>
+    <col min="1" max="1" width="62.77734375" customWidth="1"/>
+    <col min="2" max="2" width="82.77734375" customWidth="1"/>
+    <col min="3" max="4" width="14.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="F6" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="F13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="F14" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="F18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="E20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="E21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>71</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>